--- a/data/trans_dic/P3A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tareas del hogar realizadas por el/la entrevistado/a</t>
+          <t>Tareas del hogar realizadas por el/la entrevistado/a (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,85; 47,35</t>
+          <t>24,98; 46,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,88; 61,03</t>
+          <t>30,6; 59,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,47; 42,48</t>
+          <t>22,05; 43,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,52; 87,95</t>
+          <t>56,34; 88,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,92; 44,14</t>
+          <t>23,07; 44,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,98; 57,06</t>
+          <t>29,44; 58,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,78; 57,73</t>
+          <t>34,63; 57,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,85; 85,16</t>
+          <t>66,9; 85,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,65; 41,98</t>
+          <t>26,39; 42,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,96; 55,93</t>
+          <t>34,73; 54,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,5; 48,22</t>
+          <t>31,13; 47,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,3; 83,96</t>
+          <t>65,4; 83,85</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,5; 52,1</t>
+          <t>33,04; 51,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,94; 42,92</t>
+          <t>23,38; 43,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,38; 44,28</t>
+          <t>25,51; 44,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87,61; 96,92</t>
+          <t>87,44; 97,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,39; 47,3</t>
+          <t>27,67; 47,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,37; 59,03</t>
+          <t>37,72; 58,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,75; 45,91</t>
+          <t>29,57; 47,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>90,28; 97,61</t>
+          <t>89,53; 97,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,53; 47,12</t>
+          <t>32,44; 46,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,28; 47,84</t>
+          <t>32,78; 47,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,55; 43,15</t>
+          <t>30,05; 43,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,49; 96,32</t>
+          <t>90,28; 96,3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,82; 44,63</t>
+          <t>24,38; 43,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,83; 50,99</t>
+          <t>28,96; 51,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,31; 43,49</t>
+          <t>23,05; 44,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,34; 95,88</t>
+          <t>84,48; 95,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,69; 45,07</t>
+          <t>28,62; 46,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,53; 39,27</t>
+          <t>19,81; 38,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,96; 33,08</t>
+          <t>14,33; 32,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87,35; 97,28</t>
+          <t>87,83; 97,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,51; 42,3</t>
+          <t>29,26; 42,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,67; 41,88</t>
+          <t>26,26; 40,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,01; 34,89</t>
+          <t>21,08; 35,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87,78; 95,35</t>
+          <t>88,0; 95,28</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,3; 41,63</t>
+          <t>22,44; 41,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,31; 57,31</t>
+          <t>32,52; 56,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,64; 49,56</t>
+          <t>25,97; 49,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76,1; 91,64</t>
+          <t>76,47; 91,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,12; 35,51</t>
+          <t>19,9; 36,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,63; 48,77</t>
+          <t>25,81; 47,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,55; 58,99</t>
+          <t>35,08; 59,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78,17; 94,71</t>
+          <t>78,58; 94,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,17; 35,83</t>
+          <t>23,39; 35,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,67; 49,08</t>
+          <t>32,5; 48,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,68; 50,83</t>
+          <t>33,58; 50,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,24; 91,82</t>
+          <t>80,57; 91,71</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,73; 63,21</t>
+          <t>13,97; 64,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,81; 65,26</t>
+          <t>23,7; 61,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,2; 46,24</t>
+          <t>19,8; 46,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89,37; 100,0</t>
+          <t>89,41; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,68; 68,67</t>
+          <t>18,36; 66,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,08; 69,27</t>
+          <t>37,35; 70,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,87; 43,74</t>
+          <t>20,21; 46,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>82,25; 96,99</t>
+          <t>82,91; 97,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,76; 58,86</t>
+          <t>22,9; 56,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,92; 62,0</t>
+          <t>35,53; 60,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,24; 42,23</t>
+          <t>23,06; 41,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,81; 97,65</t>
+          <t>88,93; 97,67</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,68; 37,23</t>
+          <t>17,39; 37,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22,37; 45,13</t>
+          <t>21,53; 45,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,55; 50,25</t>
+          <t>21,08; 50,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84,47; 96,59</t>
+          <t>84,11; 96,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,05; 35,02</t>
+          <t>16,68; 34,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,18; 38,1</t>
+          <t>16,93; 38,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,31; 44,73</t>
+          <t>16,18; 43,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82,27; 95,62</t>
+          <t>82,79; 95,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,36; 33,78</t>
+          <t>19,83; 34,3</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,43; 38,42</t>
+          <t>22,84; 38,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,9; 41,93</t>
+          <t>22,07; 42,17</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>85,86; 94,91</t>
+          <t>86,06; 94,91</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31,57; 46,99</t>
+          <t>31,01; 46,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,23; 37,76</t>
+          <t>23,77; 37,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,63; 41,16</t>
+          <t>27,33; 41,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,72; 92,92</t>
+          <t>80,44; 92,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,36; 48,36</t>
+          <t>32,87; 48,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,75; 31,68</t>
+          <t>17,91; 31,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,32; 36,89</t>
+          <t>23,93; 37,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>79,72; 90,4</t>
+          <t>80,13; 90,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34,41; 44,93</t>
+          <t>34,8; 45,36</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23,02; 32,05</t>
+          <t>23,0; 32,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,17; 37,21</t>
+          <t>26,82; 36,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,28; 90,28</t>
+          <t>82,59; 90,38</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,44; 42,91</t>
+          <t>26,9; 43,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,58; 36,74</t>
+          <t>22,71; 36,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,21; 35,11</t>
+          <t>21,88; 34,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68,42; 80,79</t>
+          <t>68,34; 80,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,24; 48,73</t>
+          <t>33,31; 49,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,35; 40,41</t>
+          <t>27,43; 40,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,25; 35,96</t>
+          <t>23,37; 36,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>69,79; 81,84</t>
+          <t>70,26; 82,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32,64; 44,39</t>
+          <t>32,34; 44,02</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26,65; 36,01</t>
+          <t>26,64; 35,9</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,62; 33,12</t>
+          <t>24,54; 33,83</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>71,23; 80,17</t>
+          <t>70,62; 79,73</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31,87; 38,82</t>
+          <t>31,95; 38,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30,84; 37,98</t>
+          <t>30,61; 37,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,1; 35,95</t>
+          <t>29,07; 35,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82,54; 88,56</t>
+          <t>82,32; 88,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,55; 39,17</t>
+          <t>32,64; 39,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,1; 37,21</t>
+          <t>30,38; 37,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,84; 36,52</t>
+          <t>30,09; 36,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83,58; 88,14</t>
+          <t>83,7; 88,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33,33; 37,99</t>
+          <t>33,34; 38,49</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31,71; 36,52</t>
+          <t>31,76; 36,45</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30,41; 35,26</t>
+          <t>30,42; 35,31</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>83,9; 87,61</t>
+          <t>83,95; 87,82</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tareas del hogar realizadas por el/la entrevistado/a (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>16726</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11508</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14543</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56378</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16777</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23776</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>61400</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>33489</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28286</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>38319</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>117778</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>11915; 22165</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7760; 15129</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10006; 19876</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>41289; 64937</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11801; 22718</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11210; 22154</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>18004; 30043</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>53100; 67844</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>26091; 42029</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>22035; 34788</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>30312; 46305</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>99832; 127996</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>28763</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17503</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24668</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>118669</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>23905</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28168</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>30062</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>120972</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>52667</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>45671</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>54731</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>239642</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>22432; 35114</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12715; 23762</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>18035; 31133</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111623; 123906</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>17970; 30544</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>22212; 34512</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>23658; 37631</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>114235; 124540</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>43091; 61206</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>37127; 54138</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>45284; 65052</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>230436; 245808</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>21825</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21314</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19049</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52958</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24933</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17236</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>15280</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>62621</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>38550</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>34328</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>115578</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>15775; 28316</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15264; 27400</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13394; 25894</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>49223; 55925</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19431; 31274</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>11871; 22884</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9486; 21542</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>58990; 65251</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>38792; 56020</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>29577; 46148</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26200; 43868</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>110384; 119515</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>20910</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22027</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16706</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>59931</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>19985</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20371</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>22563</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>68600</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>40896</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>42398</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>39269</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>128532</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>14821; 27270</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16157; 27879</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11714; 22223</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>53637; 64181</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>14629; 26970</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>14319; 26573</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>16717; 28229</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>61394; 73729</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>32642; 49421</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>34174; 51445</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>31147; 46826</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>119469; 135987</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7495</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10436</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33462</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4889</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13071</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11094</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>37497</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8260</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>20566</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>21530</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>70959</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1333; 6116</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4276; 11060</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6412; 15085</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>30857; 34513</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2093; 7636</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9200; 17444</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7179; 16657</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>33759; 39553</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4795; 11795</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>15161; 25623</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>15653; 27881</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>66905; 73480</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>12406</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>14623</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9416</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>42605</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>13289</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>13320</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>9226</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>51007</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>25695</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>27943</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>18642</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>93613</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>8112; 17411</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9592; 20045</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>5752; 13797</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>38830; 44545</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>8718; 17885</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>8384; 18951</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>5075; 13758</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>46518; 53698</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>19616; 33930</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>21485; 36066</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>12944; 24728</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>88090; 97141</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>42921</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>35594</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>39690</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>109510</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>45176</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>29533</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>35670</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>134293</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>88097</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>65127</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>75360</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>243804</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>34308; 51077</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>27745; 43902</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>31914; 48536</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>100152; 115276</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>36419; 53366</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>21810; 38050</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>28510; 44213</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>125015; 140858</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>77051; 100449</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>54846; 76779</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>63273; 86266</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>231671; 253521</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>31117</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>33869</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>36476</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>98052</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>39743</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>43389</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>41261</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>120224</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>70860</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>77258</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>77737</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>218275</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>24259; 38843</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>26236; 41633</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>28373; 44125</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>89946; 106264</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>32173; 48094</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>35783; 52239</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>32538; 50483</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>110165; 129449</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>60387; 82211</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>65534; 88328</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>65970; 90963</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>203673; 229951</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>178038</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>163934</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>170985</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>571565</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>188683</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>181865</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>188932</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>656615</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>366721</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>345800</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>359917</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1228181</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>160825; 194731</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>146023; 180617</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>152738; 189092</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>548406; 588993</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>172522; 206363</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>163677; 200904</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>171826; 209631</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>637741; 674181</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>344083; 397200</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>322566; 370197</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>333531; 387098</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1198846; 1254226</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P3A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,98; 46,46</t>
+          <t>25,46; 46,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,6; 59,66</t>
+          <t>30,27; 60,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,05; 43,79</t>
+          <t>21,8; 43,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56,34; 88,61</t>
+          <t>57,57; 87,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,07; 44,4</t>
+          <t>22,8; 44,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,44; 58,18</t>
+          <t>31,23; 59,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,63; 57,78</t>
+          <t>34,39; 57,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,9; 85,48</t>
+          <t>66,27; 85,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,39; 42,51</t>
+          <t>26,7; 41,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,73; 54,84</t>
+          <t>34,73; 55,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,13; 47,55</t>
+          <t>31,27; 47,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,4; 83,85</t>
+          <t>66,91; 84,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,04; 51,72</t>
+          <t>33,1; 52,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,38; 43,69</t>
+          <t>22,88; 42,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,51; 44,03</t>
+          <t>26,48; 45,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87,44; 97,06</t>
+          <t>87,6; 97,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,67; 47,04</t>
+          <t>27,27; 46,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,72; 58,61</t>
+          <t>38,08; 57,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,57; 47,04</t>
+          <t>28,08; 46,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,53; 97,6</t>
+          <t>90,15; 97,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,44; 46,08</t>
+          <t>33,33; 46,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32,78; 47,8</t>
+          <t>33,5; 47,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,05; 43,17</t>
+          <t>29,92; 42,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,28; 96,3</t>
+          <t>90,01; 96,17</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,38; 43,77</t>
+          <t>24,98; 44,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,96; 51,98</t>
+          <t>29,7; 52,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,05; 44,56</t>
+          <t>22,15; 42,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,48; 95,98</t>
+          <t>83,54; 95,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,62; 46,06</t>
+          <t>27,62; 46,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,81; 38,18</t>
+          <t>19,19; 38,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,33; 32,55</t>
+          <t>15,42; 32,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87,83; 97,15</t>
+          <t>86,41; 97,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,26; 42,25</t>
+          <t>29,09; 42,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,26; 40,97</t>
+          <t>26,96; 41,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,08; 35,3</t>
+          <t>21,1; 34,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>88,0; 95,28</t>
+          <t>87,76; 95,55</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,44; 41,28</t>
+          <t>23,1; 41,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,52; 56,12</t>
+          <t>32,3; 56,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,97; 49,26</t>
+          <t>24,95; 49,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76,47; 91,5</t>
+          <t>75,8; 92,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,9; 36,69</t>
+          <t>19,33; 35,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,81; 47,9</t>
+          <t>25,81; 48,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,08; 59,24</t>
+          <t>35,26; 59,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78,58; 94,36</t>
+          <t>78,44; 94,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,39; 35,41</t>
+          <t>23,72; 36,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,5; 48,92</t>
+          <t>33,05; 49,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,58; 50,48</t>
+          <t>34,23; 51,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,57; 91,71</t>
+          <t>80,24; 91,76</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,97; 64,11</t>
+          <t>13,64; 63,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,7; 61,3</t>
+          <t>23,63; 63,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,8; 46,59</t>
+          <t>19,55; 45,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89,41; 100,0</t>
+          <t>89,02; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,36; 66,98</t>
+          <t>18,33; 67,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,35; 70,82</t>
+          <t>36,12; 68,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,21; 46,9</t>
+          <t>19,81; 45,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>82,91; 97,14</t>
+          <t>84,06; 97,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,9; 56,33</t>
+          <t>22,83; 56,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35,53; 60,04</t>
+          <t>34,24; 61,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,06; 41,07</t>
+          <t>22,77; 40,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,93; 97,67</t>
+          <t>89,18; 97,72</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,39; 37,32</t>
+          <t>17,25; 38,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,53; 45,0</t>
+          <t>21,02; 44,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,08; 50,57</t>
+          <t>21,81; 50,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84,11; 96,49</t>
+          <t>85,11; 97,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,68; 34,22</t>
+          <t>16,77; 35,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,93; 38,26</t>
+          <t>17,46; 38,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,18; 43,88</t>
+          <t>17,03; 45,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82,79; 95,57</t>
+          <t>82,94; 95,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,83; 34,3</t>
+          <t>20,05; 34,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,84; 38,34</t>
+          <t>21,32; 38,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,07; 42,17</t>
+          <t>22,78; 42,64</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>86,06; 94,91</t>
+          <t>85,86; 94,99</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31,01; 46,16</t>
+          <t>31,63; 47,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,77; 37,62</t>
+          <t>23,78; 37,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,33; 41,57</t>
+          <t>27,59; 41,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,44; 92,59</t>
+          <t>80,79; 92,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,87; 48,17</t>
+          <t>33,7; 48,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,91; 31,25</t>
+          <t>18,42; 31,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,93; 37,12</t>
+          <t>23,66; 37,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>80,13; 90,29</t>
+          <t>80,44; 90,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34,8; 45,36</t>
+          <t>34,34; 44,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23,0; 32,2</t>
+          <t>22,73; 32,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26,82; 36,57</t>
+          <t>27,26; 37,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,59; 90,38</t>
+          <t>82,69; 90,27</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,9; 43,08</t>
+          <t>27,05; 43,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22,71; 36,03</t>
+          <t>22,93; 36,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,88; 34,03</t>
+          <t>21,99; 34,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68,34; 80,74</t>
+          <t>67,95; 80,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,31; 49,8</t>
+          <t>33,91; 49,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,43; 40,04</t>
+          <t>26,81; 40,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,37; 36,26</t>
+          <t>23,77; 36,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>70,26; 82,56</t>
+          <t>70,12; 81,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32,34; 44,02</t>
+          <t>32,72; 43,91</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26,64; 35,9</t>
+          <t>26,78; 36,12</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,54; 33,83</t>
+          <t>24,66; 33,69</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>70,62; 79,73</t>
+          <t>71,34; 79,59</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31,95; 38,69</t>
+          <t>32,07; 38,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30,61; 37,87</t>
+          <t>31,15; 38,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,07; 35,99</t>
+          <t>29,41; 36,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82,32; 88,42</t>
+          <t>82,55; 88,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,64; 39,04</t>
+          <t>32,32; 39,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,38; 37,29</t>
+          <t>30,72; 37,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,09; 36,71</t>
+          <t>29,98; 36,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83,7; 88,48</t>
+          <t>83,6; 88,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33,34; 38,49</t>
+          <t>33,31; 37,76</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31,76; 36,45</t>
+          <t>31,8; 36,78</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30,42; 35,31</t>
+          <t>30,49; 34,92</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>83,95; 87,82</t>
+          <t>84,1; 87,7</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11915; 22165</t>
+          <t>12145; 22293</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7760; 15129</t>
+          <t>7675; 15240</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10006; 19876</t>
+          <t>9895; 19560</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41289; 64937</t>
+          <t>42191; 64224</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11801; 22718</t>
+          <t>11664; 22712</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11210; 22154</t>
+          <t>11891; 22476</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18004; 30043</t>
+          <t>17882; 30116</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53100; 67844</t>
+          <t>52594; 67542</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26091; 42029</t>
+          <t>26400; 41264</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22035; 34788</t>
+          <t>22031; 35221</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30312; 46305</t>
+          <t>30455; 46185</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>99832; 127996</t>
+          <t>102138; 129535</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22432; 35114</t>
+          <t>22472; 35346</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12715; 23762</t>
+          <t>12442; 22901</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18035; 31133</t>
+          <t>18719; 31822</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111623; 123906</t>
+          <t>111824; 123864</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17970; 30544</t>
+          <t>17708; 29966</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22212; 34512</t>
+          <t>22426; 33769</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23658; 37631</t>
+          <t>22459; 36946</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>114235; 124540</t>
+          <t>115027; 124764</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43091; 61206</t>
+          <t>44272; 62120</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37127; 54138</t>
+          <t>37943; 53977</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45284; 65052</t>
+          <t>45085; 64126</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>230436; 245808</t>
+          <t>229750; 245481</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15775; 28316</t>
+          <t>16158; 28632</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15264; 27400</t>
+          <t>15656; 27929</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13394; 25894</t>
+          <t>12870; 24940</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49223; 55925</t>
+          <t>48677; 55701</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19431; 31274</t>
+          <t>18753; 31273</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11871; 22884</t>
+          <t>11498; 22874</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9486; 21542</t>
+          <t>10205; 21243</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>58990; 65251</t>
+          <t>58038; 65222</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38792; 56020</t>
+          <t>38573; 56568</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29577; 46148</t>
+          <t>30372; 47015</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26200; 43868</t>
+          <t>26229; 43058</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>110384; 119515</t>
+          <t>110077; 119855</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14821; 27270</t>
+          <t>15256; 27310</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16157; 27879</t>
+          <t>16047; 27962</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11714; 22223</t>
+          <t>11254; 22114</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53637; 64181</t>
+          <t>53171; 64657</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14629; 26970</t>
+          <t>14214; 26192</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14319; 26573</t>
+          <t>14317; 26997</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16717; 28229</t>
+          <t>16803; 28377</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61394; 73729</t>
+          <t>61291; 73749</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32642; 49421</t>
+          <t>33110; 50563</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34174; 51445</t>
+          <t>34753; 51701</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31147; 46826</t>
+          <t>31753; 47614</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>119469; 135987</t>
+          <t>118975; 136064</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1333; 6116</t>
+          <t>1301; 6089</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4276; 11060</t>
+          <t>4264; 11497</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6412; 15085</t>
+          <t>6328; 14790</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30857; 34513</t>
+          <t>30724; 34513</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2093; 7636</t>
+          <t>2090; 7686</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9200; 17444</t>
+          <t>8896; 16821</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7179; 16657</t>
+          <t>7036; 16119</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33759; 39553</t>
+          <t>34228; 39550</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4795; 11795</t>
+          <t>4780; 11907</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15161; 25623</t>
+          <t>14613; 26070</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15653; 27881</t>
+          <t>15457; 27739</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>66905; 73480</t>
+          <t>67093; 73513</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8112; 17411</t>
+          <t>8049; 17808</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9592; 20045</t>
+          <t>9363; 19998</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5752; 13797</t>
+          <t>5949; 13713</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38830; 44545</t>
+          <t>39295; 44880</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8718; 17885</t>
+          <t>8766; 18474</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8384; 18951</t>
+          <t>8650; 19025</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5075; 13758</t>
+          <t>5340; 14398</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>46518; 53698</t>
+          <t>46603; 53677</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19616; 33930</t>
+          <t>19837; 34212</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21485; 36066</t>
+          <t>20058; 36512</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12944; 24728</t>
+          <t>13355; 25002</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>88090; 97141</t>
+          <t>87881; 97229</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34308; 51077</t>
+          <t>34994; 52037</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27745; 43902</t>
+          <t>27749; 44134</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31914; 48536</t>
+          <t>32213; 48316</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100152; 115276</t>
+          <t>100584; 115070</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>36419; 53366</t>
+          <t>37335; 53869</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21810; 38050</t>
+          <t>22434; 38247</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28510; 44213</t>
+          <t>28189; 44874</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>125015; 140858</t>
+          <t>125490; 141792</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>77051; 100449</t>
+          <t>76041; 99483</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54846; 76779</t>
+          <t>54211; 76597</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63273; 86266</t>
+          <t>64310; 87998</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>231671; 253521</t>
+          <t>231954; 253213</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>24259; 38843</t>
+          <t>24387; 38903</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>26236; 41633</t>
+          <t>26497; 42405</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28373; 44125</t>
+          <t>28509; 44410</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>89946; 106264</t>
+          <t>89432; 106165</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>32173; 48094</t>
+          <t>32753; 47533</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>35783; 52239</t>
+          <t>34975; 53197</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>32538; 50483</t>
+          <t>33087; 50497</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>110165; 129449</t>
+          <t>109937; 128327</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>60387; 82211</t>
+          <t>61102; 82008</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>65534; 88328</t>
+          <t>65873; 88863</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>65970; 90963</t>
+          <t>66297; 90580</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>203673; 229951</t>
+          <t>205758; 229557</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>160825; 194731</t>
+          <t>161434; 195904</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>146023; 180617</t>
+          <t>148578; 181319</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>152738; 189092</t>
+          <t>154519; 189234</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>548406; 588993</t>
+          <t>549921; 590002</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>172522; 206363</t>
+          <t>170832; 207188</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>163677; 200904</t>
+          <t>165504; 202389</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>171826; 209631</t>
+          <t>171223; 207722</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>637741; 674181</t>
+          <t>637030; 673605</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>344083; 397200</t>
+          <t>343708; 389694</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>322566; 370197</t>
+          <t>323044; 373546</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>333531; 387098</t>
+          <t>334332; 382916</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1198846; 1254226</t>
+          <t>1200986; 1252460</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32,76%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>44,06%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>45,73%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>79,38%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>35,06%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>45,39%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>32,04%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>76,93%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32,76%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,73%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,46; 46,73</t>
+          <t>22,92; 44,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,27; 60,1</t>
+          <t>29,98; 57,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,8; 43,1</t>
+          <t>34,78; 57,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57,57; 87,64</t>
+          <t>70,29; 86,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,8; 44,39</t>
+          <t>24,85; 47,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,23; 59,02</t>
+          <t>30,88; 61,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,39; 57,92</t>
+          <t>21,47; 42,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,27; 85,1</t>
+          <t>74,54; 90,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,7; 41,74</t>
+          <t>25,65; 41,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,73; 55,52</t>
+          <t>34,96; 55,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,27; 47,43</t>
+          <t>31,5; 48,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,91; 84,86</t>
+          <t>75,74; 86,54</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36,81%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>47,83%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37,58%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>94,64%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>42,37%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>32,18%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>34,89%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>92,96%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,81%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>47,83%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>37,58%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,1; 52,07</t>
+          <t>27,39; 47,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,88; 42,11</t>
+          <t>37,37; 59,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,48; 45,01</t>
+          <t>28,75; 45,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87,6; 97,03</t>
+          <t>89,8; 97,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,27; 46,15</t>
+          <t>32,5; 52,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,08; 57,35</t>
+          <t>22,94; 42,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,08; 46,19</t>
+          <t>26,38; 44,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>90,15; 97,78</t>
+          <t>85,9; 95,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,33; 46,77</t>
+          <t>32,53; 47,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,5; 47,65</t>
+          <t>33,28; 47,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,92; 42,55</t>
+          <t>29,55; 43,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,01; 96,17</t>
+          <t>89,9; 95,6</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>36,72%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28,76%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23,09%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>92,65%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>33,73%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>40,43%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>32,78%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>90,89%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>36,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,09%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,98; 44,26</t>
+          <t>27,69; 45,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,7; 52,98</t>
+          <t>19,53; 39,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,15; 42,92</t>
+          <t>15,96; 33,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,54; 95,59</t>
+          <t>86,49; 97,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,62; 46,06</t>
+          <t>24,82; 44,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,19; 38,17</t>
+          <t>29,83; 50,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,42; 32,1</t>
+          <t>23,31; 43,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86,41; 97,11</t>
+          <t>82,68; 95,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,09; 42,66</t>
+          <t>28,51; 42,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,96; 41,74</t>
+          <t>27,67; 41,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,1; 34,64</t>
+          <t>21,01; 34,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87,76; 95,55</t>
+          <t>86,86; 94,93</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36,72%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>47,35%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>86,39%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>31,66%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>44,34%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>37,03%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>85,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>36,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>47,35%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,12%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,1; 41,34</t>
+          <t>19,12; 35,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,3; 56,28</t>
+          <t>25,63; 48,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,95; 49,02</t>
+          <t>35,55; 58,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75,8; 92,18</t>
+          <t>75,76; 93,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,33; 35,63</t>
+          <t>23,3; 41,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,81; 48,67</t>
+          <t>33,31; 57,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,26; 59,55</t>
+          <t>25,64; 49,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78,44; 94,39</t>
+          <t>76,91; 92,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,72; 36,23</t>
+          <t>23,17; 35,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,05; 49,17</t>
+          <t>32,67; 49,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,23; 51,33</t>
+          <t>33,68; 50,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,24; 91,76</t>
+          <t>79,74; 91,6</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>42,89%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53,07%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>31,24%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>35,33%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>41,54%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>32,24%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>42,89%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>53,07%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>31,24%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,64; 63,82</t>
+          <t>18,68; 68,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,63; 63,72</t>
+          <t>37,08; 69,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,55; 45,68</t>
+          <t>18,87; 43,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89,02; 100,0</t>
+          <t>81,77; 96,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,33; 67,43</t>
+          <t>13,73; 63,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,12; 68,3</t>
+          <t>23,81; 65,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,81; 45,39</t>
+          <t>19,2; 46,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,06; 97,13</t>
+          <t>89,87; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,83; 56,86</t>
+          <t>22,76; 58,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,24; 61,09</t>
+          <t>34,92; 62,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,77; 40,86</t>
+          <t>23,24; 42,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,18; 97,72</t>
+          <t>88,96; 97,68</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26,89%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29,42%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>90,12%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>26,59%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>32,83%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>34,51%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92,28%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>25,42%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>29,42%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,25; 38,17</t>
+          <t>17,05; 35,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,02; 44,9</t>
+          <t>17,18; 38,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,81; 50,26</t>
+          <t>16,31; 44,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85,11; 97,21</t>
+          <t>81,36; 95,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,77; 35,34</t>
+          <t>16,68; 37,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,46; 38,41</t>
+          <t>22,37; 45,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,03; 45,92</t>
+          <t>20,55; 50,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82,94; 95,53</t>
+          <t>86,03; 97,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,05; 34,58</t>
+          <t>19,36; 33,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21,32; 38,81</t>
+          <t>22,43; 38,42</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,78; 42,64</t>
+          <t>21,9; 41,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>85,86; 94,99</t>
+          <t>86,45; 95,01</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40,78%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24,25%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>29,94%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>85,61%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>38,79%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>30,5%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>33,99%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>87,95%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>40,78%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>29,94%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31,63; 47,03</t>
+          <t>33,36; 48,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,78; 37,82</t>
+          <t>18,75; 31,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,59; 41,38</t>
+          <t>23,32; 36,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,79; 92,42</t>
+          <t>79,34; 90,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,7; 48,62</t>
+          <t>31,57; 46,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,42; 31,41</t>
+          <t>24,23; 37,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,66; 37,67</t>
+          <t>27,63; 41,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>80,44; 90,89</t>
+          <t>83,94; 93,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34,34; 44,93</t>
+          <t>34,41; 44,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22,73; 32,12</t>
+          <t>23,02; 32,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,26; 37,31</t>
+          <t>27,17; 37,21</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,69; 90,27</t>
+          <t>83,56; 90,85</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>41,15%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33,26%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>29,64%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>76,82%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>34,51%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>29,31%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>28,13%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>74,5%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>41,15%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>33,26%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>29,64%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,9%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,05; 43,15</t>
+          <t>33,24; 48,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22,93; 36,7</t>
+          <t>27,35; 40,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,99; 34,25</t>
+          <t>23,25; 35,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67,95; 80,66</t>
+          <t>69,96; 82,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,91; 49,22</t>
+          <t>27,44; 42,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,81; 40,77</t>
+          <t>23,58; 36,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,77; 36,27</t>
+          <t>22,21; 35,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>70,12; 81,84</t>
+          <t>68,62; 81,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32,72; 43,91</t>
+          <t>32,64; 44,39</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26,78; 36,12</t>
+          <t>26,65; 36,01</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,66; 33,69</t>
+          <t>24,62; 33,12</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>71,34; 79,59</t>
+          <t>71,18; 80,27</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>33,75%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>33,09%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>85,88%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>35,37%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>34,37%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>32,54%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>85,8%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>35,7%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>33,75%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>33,09%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32,07; 38,92</t>
+          <t>32,55; 39,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,15; 38,02</t>
+          <t>30,1; 37,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,41; 36,02</t>
+          <t>29,84; 36,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82,55; 88,57</t>
+          <t>83,24; 87,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,32; 39,2</t>
+          <t>31,87; 38,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,72; 37,56</t>
+          <t>30,84; 37,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,98; 36,38</t>
+          <t>29,1; 35,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83,6; 88,4</t>
+          <t>84,06; 88,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33,31; 37,76</t>
+          <t>33,33; 37,99</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31,8; 36,78</t>
+          <t>31,71; 36,52</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30,49; 34,92</t>
+          <t>30,41; 35,26</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>84,1; 87,7</t>
+          <t>84,51; 87,73</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,37 +2073,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16777</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23776</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50918</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>16726</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>11508</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>14543</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56378</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>16763</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16777</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>23776</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61400</t>
+          <t>47612</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>117778</t>
+          <t>98529</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12145; 22293</t>
+          <t>11727; 22582</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7675; 15240</t>
+          <t>11418; 21730</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9895; 19560</t>
+          <t>18082; 30015</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42191; 64224</t>
+          <t>45086; 55345</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11664; 22712</t>
+          <t>11855; 22591</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11891; 22476</t>
+          <t>7830; 15477</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17882; 30116</t>
+          <t>9746; 19281</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52594; 67542</t>
+          <t>42102; 51127</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26400; 41264</t>
+          <t>25360; 41503</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22031; 35221</t>
+          <t>22175; 35482</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30455; 46185</t>
+          <t>30673; 46954</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>102138; 129535</t>
+          <t>91363; 104391</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>129</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23905</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28168</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30062</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>109628</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>28763</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>17503</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>24668</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>118669</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>23905</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28168</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30062</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>120972</t>
+          <t>92965</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>239642</t>
+          <t>202593</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22472; 35346</t>
+          <t>17784; 30712</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12442; 22901</t>
+          <t>22006; 34761</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18719; 31822</t>
+          <t>23001; 36725</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111824; 123864</t>
+          <t>104020; 113046</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17708; 29966</t>
+          <t>22067; 35368</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22426; 33769</t>
+          <t>12476; 23342</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22459; 36946</t>
+          <t>18652; 31305</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>115027; 124764</t>
+          <t>87100; 96645</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44272; 62120</t>
+          <t>43203; 62578</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37943; 53977</t>
+          <t>37692; 54194</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45085; 64126</t>
+          <t>44527; 65026</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>229750; 245481</t>
+          <t>195295; 207682</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>88</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>24933</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17236</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15280</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>55014</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>21825</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>21314</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>19049</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>52958</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>24933</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17236</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15280</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62621</t>
+          <t>51163</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>115578</t>
+          <t>106178</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16158; 28632</t>
+          <t>18803; 30604</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15656; 27929</t>
+          <t>11702; 23537</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12870; 24940</t>
+          <t>10563; 21892</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48677; 55701</t>
+          <t>51353; 57609</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18753; 31273</t>
+          <t>16058; 28877</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11498; 22874</t>
+          <t>15725; 26876</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10205; 21243</t>
+          <t>13546; 25275</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>58038; 65222</t>
+          <t>46761; 54103</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38573; 56568</t>
+          <t>37799; 56085</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30372; 47015</t>
+          <t>31165; 47179</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26229; 43058</t>
+          <t>26111; 43360</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>110077; 119855</t>
+          <t>100704; 110053</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>81</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19985</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20371</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22563</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>62340</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>20910</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>22027</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>16706</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>59931</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19985</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20371</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22563</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>68600</t>
+          <t>60820</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>128532</t>
+          <t>123159</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15256; 27310</t>
+          <t>14058; 26105</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16047; 27962</t>
+          <t>14219; 27051</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11254; 22114</t>
+          <t>16941; 28107</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53171; 64657</t>
+          <t>54667; 67503</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14214; 26192</t>
+          <t>15391; 27497</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14317; 26997</t>
+          <t>16547; 28471</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16803; 28377</t>
+          <t>11565; 22360</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61291; 73749</t>
+          <t>54483; 65181</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33110; 50563</t>
+          <t>32337; 50001</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34753; 51701</t>
+          <t>34355; 51607</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31753; 47614</t>
+          <t>31246; 47156</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>118975; 136064</t>
+          <t>114029; 130986</t>
         </is>
       </c>
     </row>
@@ -2905,32 +2905,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4889</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13071</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11094</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>36367</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3370</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>7495</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>10436</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33462</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4889</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13071</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11094</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37497</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70959</t>
+          <t>70969</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1301; 6089</t>
+          <t>2129; 7828</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4264; 11497</t>
+          <t>9134; 17061</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6328; 14790</t>
+          <t>6702; 15534</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30724; 34513</t>
+          <t>32364; 38347</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2090; 7686</t>
+          <t>1310; 6031</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8896; 16821</t>
+          <t>4296; 11775</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7036; 16119</t>
+          <t>6215; 14969</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34228; 39550</t>
+          <t>32002; 35608</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4780; 11907</t>
+          <t>4766; 12327</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14613; 26070</t>
+          <t>14903; 26457</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15457; 27739</t>
+          <t>15775; 28669</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>67093; 73513</t>
+          <t>66888; 73442</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>73</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>13289</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13320</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9226</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>44107</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>12406</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>14623</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>9416</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>42605</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>13289</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13320</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9226</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>42582</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93613</t>
+          <t>86689</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8049; 17808</t>
+          <t>8913; 18307</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9363; 19998</t>
+          <t>8508; 18874</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5949; 13713</t>
+          <t>5114; 14025</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39295; 44880</t>
+          <t>39818; 46673</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8766; 18474</t>
+          <t>7781; 17373</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8650; 19025</t>
+          <t>9964; 20101</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5340; 14398</t>
+          <t>5605; 13711</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>46603; 53677</t>
+          <t>39372; 44602</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19837; 34212</t>
+          <t>19149; 33422</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20058; 36512</t>
+          <t>21105; 36144</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13355; 25002</t>
+          <t>12843; 24588</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>87881; 97229</t>
+          <t>81873; 89984</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>159</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>45176</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>29533</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>35670</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>121020</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>42921</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>35594</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>39690</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>109510</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>45176</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>29533</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>35670</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>134293</t>
+          <t>110039</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>243804</t>
+          <t>231058</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34994; 52037</t>
+          <t>36954; 53572</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27749; 44134</t>
+          <t>22831; 38577</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32213; 48316</t>
+          <t>27775; 43945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100584; 115070</t>
+          <t>112163; 127623</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>37335; 53869</t>
+          <t>34935; 51990</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22434; 38247</t>
+          <t>28283; 44062</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28189; 44874</t>
+          <t>32261; 48063</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>125490; 141792</t>
+          <t>102852; 114764</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>76041; 99483</t>
+          <t>76199; 99496</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54211; 76597</t>
+          <t>54894; 76441</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64310; 87998</t>
+          <t>64098; 87776</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>231954; 253213</t>
+          <t>220500; 239748</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>139</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>39743</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>43389</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>41261</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>122472</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>31117</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>33869</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>36476</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>98052</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>39743</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>43389</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>41261</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>120224</t>
+          <t>105168</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>218275</t>
+          <t>227639</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>24387; 38903</t>
+          <t>32102; 47057</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>26497; 42405</t>
+          <t>35678; 52728</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28509; 44410</t>
+          <t>32372; 50060</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>89432; 106165</t>
+          <t>111535; 131062</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>32753; 47533</t>
+          <t>24744; 38695</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34975; 53197</t>
+          <t>27248; 42446</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33087; 50497</t>
+          <t>28790; 45528</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>109937; 128327</t>
+          <t>96412; 114243</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>61102; 82008</t>
+          <t>60962; 82898</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>65873; 88863</t>
+          <t>65569; 88586</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>66297; 90580</t>
+          <t>66198; 89064</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>205758; 229557</t>
+          <t>213469; 240745</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>253</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>816</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>839</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>188683</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>181865</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>188932</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>601865</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>178038</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>163934</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>170985</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>571565</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>188683</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>181865</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>188932</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>656615</t>
+          <t>544949</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1228181</t>
+          <t>1146816</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>161434; 195904</t>
+          <t>172022; 207056</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>148578; 181319</t>
+          <t>162166; 200479</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>154519; 189234</t>
+          <t>170425; 208535</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>549921; 590002</t>
+          <t>583378; 616585</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>170832; 207188</t>
+          <t>160422; 195426</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>165504; 202389</t>
+          <t>147102; 181161</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>171223; 207722</t>
+          <t>152883; 188892</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>637030; 673605</t>
+          <t>529290; 559406</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>343708; 389694</t>
+          <t>343940; 392042</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>323044; 373546</t>
+          <t>322120; 370964</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>334332; 382916</t>
+          <t>333384; 386607</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1200986; 1252460</t>
+          <t>1124354; 1167240</t>
         </is>
       </c>
     </row>
